--- a/web/public/forms/hasugwangeo-sigong.xlsx
+++ b/web/public/forms/hasugwangeo-sigong.xlsx
@@ -1267,7 +1267,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="64" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="64" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="64" t="inlineStr">
@@ -5565,7 +5565,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="64" t="inlineStr">
@@ -6525,7 +6525,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="64" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="64" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -10056,7 +10056,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -14081,7 +14081,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">

--- a/web/public/forms/hasugwangeo-sigong.xlsx
+++ b/web/public/forms/hasugwangeo-sigong.xlsx
@@ -20,12 +20,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.일일시공일정" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.장비인력투입" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.안전환경관리" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-표지" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-1.공사개요" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-2.위치도" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-4.예정공정표" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-6.일일시공일정" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-7.장비인력투입" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$L$8</definedName>
@@ -41,12 +35,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'6.일일시공일정'!$A$1:$L$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'7.장비인력투입'!$A$1:$L$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'8.안전환경관리'!$A$1:$L$63</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'예시-표지'!$A$1:$L$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'예시-1.공사개요'!$A$1:$L$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'예시-2.위치도'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'예시-4.예정공정표'!$A$1:$AC$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'예시-6.일일시공일정'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'예시-7.장비인력투입'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -312,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -495,32 +483,10 @@
     <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0;;&quot;&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="301" formatCode="#,##0&quot; m&quot;;;&quot;&quot;"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="002F5597"/>
-          <bgColor rgb="002F5597"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="302" formatCode="#,##0&quot; m/일&quot;;;&quot;&quot;"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1325,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -2138,10 +2105,7 @@
         <v>0.3125</v>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="53">
-        <f>IF(OR(A7="",C7=""),"",IF(C7&lt;A7,"⚠",ROUND((C7-A7)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E7" s="53" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="28" t="inlineStr">
         <is>
@@ -2163,10 +2127,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="53">
-        <f>IF(OR(A8="",C8=""),"",IF(C8&lt;A8,"⚠",ROUND((C8-A8)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E8" s="53" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="28" t="inlineStr">
         <is>
@@ -2188,10 +2149,7 @@
         <v>0.375</v>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="53">
-        <f>IF(OR(A9="",C9=""),"",IF(C9&lt;A9,"⚠",ROUND((C9-A9)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E9" s="53" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="28" t="inlineStr">
         <is>
@@ -2213,10 +2171,7 @@
         <v>0.5</v>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="53">
-        <f>IF(OR(A10="",C10=""),"",IF(C10&lt;A10,"⚠",ROUND((C10-A10)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E10" s="53" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="28" t="inlineStr">
         <is>
@@ -2238,10 +2193,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="53">
-        <f>IF(OR(A11="",C11=""),"",IF(C11&lt;A11,"⚠",ROUND((C11-A11)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E11" s="53" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="28" t="inlineStr">
         <is>
@@ -2263,10 +2215,7 @@
         <v>0.625</v>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="53">
-        <f>IF(OR(A12="",C12=""),"",IF(C12&lt;A12,"⚠",ROUND((C12-A12)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E12" s="53" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="28" t="inlineStr">
         <is>
@@ -2288,10 +2237,7 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="53">
-        <f>IF(OR(A13="",C13=""),"",IF(C13&lt;A13,"⚠",ROUND((C13-A13)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E13" s="53" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="28" t="inlineStr">
         <is>
@@ -2313,10 +2259,7 @@
         <v>0.6875</v>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="53">
-        <f>IF(OR(A14="",C14=""),"",IF(C14&lt;A14,"⚠",ROUND((C14-A14)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E14" s="53" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="28" t="inlineStr">
         <is>
@@ -2338,10 +2281,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="53">
-        <f>IF(OR(A15="",C15=""),"",IF(C15&lt;A15,"⚠",ROUND((C15-A15)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E15" s="53" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="28" t="inlineStr">
         <is>
@@ -2359,10 +2299,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="52" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="53">
-        <f>IF(OR(A16="",C16=""),"",IF(C16&lt;A16,"⚠",ROUND((C16-A16)*24*60,0)))</f>
-        <v/>
-      </c>
+      <c r="E16" s="53" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="6" t="n"/>
@@ -2380,10 +2317,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="54">
-        <f>IF(OR(COUNT(A7:A16)=0,COUNT(C7:C16)=0),"",ROUND((MAX(C7:C16)-MIN(A7:A16))*24,2))</f>
-        <v/>
-      </c>
+      <c r="E17" s="54" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="25" t="inlineStr"/>
       <c r="H17" s="6" t="n"/>
@@ -2410,10 +2344,7 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="55">
-        <f>IF(N('1.공사개요'!I21)=0,"",'1.공사개요'!I21)</f>
-        <v/>
-      </c>
+      <c r="E21" s="55" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -2445,10 +2376,7 @@
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
-      <c r="K22" s="58">
-        <f>IF(OR(N(E21)=0,N(K21)=0,N(E22)=0),"",ROUNDUP(E21/(K21*E22),0))</f>
-        <v/>
-      </c>
+      <c r="K22" s="58" t="n"/>
       <c r="L22" s="6" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
@@ -2458,6 +2386,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -2530,16 +2459,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G7:L7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(ISNUMBER(E21),MOD(E21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K21">
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(ISNUMBER(K21),MOD(K21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2653,10 +2572,7 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="59" t="n"/>
       <c r="F7" s="59" t="n"/>
-      <c r="G7" s="60">
-        <f>IF(OR(N(E7)=0,N(F7)=0),"",E7*F7)</f>
-        <v/>
-      </c>
+      <c r="G7" s="60" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="24" t="inlineStr">
         <is>
@@ -2682,10 +2598,7 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="59" t="n"/>
       <c r="F8" s="59" t="n"/>
-      <c r="G8" s="60">
-        <f>IF(OR(N(E8)=0,N(F8)=0),"",E8*F8)</f>
-        <v/>
-      </c>
+      <c r="G8" s="60" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="24" t="inlineStr">
         <is>
@@ -2711,10 +2624,7 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="59" t="n"/>
       <c r="F9" s="59" t="n"/>
-      <c r="G9" s="60">
-        <f>IF(OR(N(E9)=0,N(F9)=0),"",E9*F9)</f>
-        <v/>
-      </c>
+      <c r="G9" s="60" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2740,10 +2650,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="59" t="n"/>
-      <c r="G10" s="60">
-        <f>IF(OR(N(E10)=0,N(F10)=0),"",E10*F10)</f>
-        <v/>
-      </c>
+      <c r="G10" s="60" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="24" t="inlineStr">
         <is>
@@ -2769,10 +2676,7 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="59" t="n"/>
       <c r="F11" s="59" t="n"/>
-      <c r="G11" s="60">
-        <f>IF(OR(N(E11)=0,N(F11)=0),"",E11*F11)</f>
-        <v/>
-      </c>
+      <c r="G11" s="60" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="24" t="inlineStr">
         <is>
@@ -2798,10 +2702,7 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="59" t="n"/>
       <c r="F12" s="59" t="n"/>
-      <c r="G12" s="60">
-        <f>IF(OR(N(E12)=0,N(F12)=0),"",E12*F12)</f>
-        <v/>
-      </c>
+      <c r="G12" s="60" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="24" t="inlineStr">
         <is>
@@ -2827,10 +2728,7 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="59" t="n"/>
       <c r="F13" s="59" t="n"/>
-      <c r="G13" s="60">
-        <f>IF(OR(N(E13)=0,N(F13)=0),"",E13*F13)</f>
-        <v/>
-      </c>
+      <c r="G13" s="60" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="24" t="inlineStr">
         <is>
@@ -2856,10 +2754,7 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="59" t="n"/>
       <c r="F14" s="59" t="n"/>
-      <c r="G14" s="60">
-        <f>IF(OR(N(E14)=0,N(F14)=0),"",E14*F14)</f>
-        <v/>
-      </c>
+      <c r="G14" s="60" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="24" t="inlineStr">
         <is>
@@ -2885,10 +2780,7 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="59" t="n"/>
       <c r="F15" s="59" t="n"/>
-      <c r="G15" s="60">
-        <f>IF(OR(N(E15)=0,N(F15)=0),"",E15*F15)</f>
-        <v/>
-      </c>
+      <c r="G15" s="60" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="24" t="inlineStr">
         <is>
@@ -2914,10 +2806,7 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="59" t="n"/>
       <c r="F16" s="59" t="n"/>
-      <c r="G16" s="60">
-        <f>IF(OR(N(E16)=0,N(F16)=0),"",E16*F16)</f>
-        <v/>
-      </c>
+      <c r="G16" s="60" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="24" t="inlineStr">
         <is>
@@ -2943,10 +2832,7 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="59" t="n"/>
       <c r="F17" s="59" t="n"/>
-      <c r="G17" s="60">
-        <f>IF(OR(N(E17)=0,N(F17)=0),"",E17*F17)</f>
-        <v/>
-      </c>
+      <c r="G17" s="60" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="24" t="inlineStr">
         <is>
@@ -2972,10 +2858,7 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="59" t="n"/>
       <c r="F18" s="59" t="n"/>
-      <c r="G18" s="60">
-        <f>IF(OR(N(E18)=0,N(F18)=0),"",E18*F18)</f>
-        <v/>
-      </c>
+      <c r="G18" s="60" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="24" t="inlineStr">
         <is>
@@ -2993,10 +2876,7 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="59" t="n"/>
       <c r="F19" s="59" t="n"/>
-      <c r="G19" s="60">
-        <f>IF(OR(N(E19)=0,N(F19)=0),"",E19*F19)</f>
-        <v/>
-      </c>
+      <c r="G19" s="60" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="24" t="n"/>
       <c r="J19" s="6" t="n"/>
@@ -3010,10 +2890,7 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="59" t="n"/>
       <c r="F20" s="59" t="n"/>
-      <c r="G20" s="60">
-        <f>IF(OR(N(E20)=0,N(F20)=0),"",E20*F20)</f>
-        <v/>
-      </c>
+      <c r="G20" s="60" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="24" t="n"/>
       <c r="J20" s="6" t="n"/>
@@ -3031,10 +2908,7 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="61">
-        <f>IF(SUM(G7:G20)=0,"",SUM(G7:G20))</f>
-        <v/>
-      </c>
+      <c r="G21" s="61" t="n"/>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="25" t="inlineStr"/>
       <c r="J21" s="6" t="n"/>
@@ -3096,10 +2970,7 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="59" t="n"/>
       <c r="D26" s="59" t="n"/>
-      <c r="E26" s="60">
-        <f>IF(OR(N(C26)=0,N(D26)=0),"",C26*D26)</f>
-        <v/>
-      </c>
+      <c r="E26" s="60" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="24" t="inlineStr">
         <is>
@@ -3121,10 +2992,7 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="59" t="n"/>
       <c r="D27" s="59" t="n"/>
-      <c r="E27" s="60">
-        <f>IF(OR(N(C27)=0,N(D27)=0),"",C27*D27)</f>
-        <v/>
-      </c>
+      <c r="E27" s="60" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="24" t="inlineStr">
         <is>
@@ -3146,10 +3014,7 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="59" t="n"/>
       <c r="D28" s="59" t="n"/>
-      <c r="E28" s="60">
-        <f>IF(OR(N(C28)=0,N(D28)=0),"",C28*D28)</f>
-        <v/>
-      </c>
+      <c r="E28" s="60" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="24" t="inlineStr">
         <is>
@@ -3171,10 +3036,7 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="59" t="n"/>
       <c r="D29" s="59" t="n"/>
-      <c r="E29" s="60">
-        <f>IF(OR(N(C29)=0,N(D29)=0),"",C29*D29)</f>
-        <v/>
-      </c>
+      <c r="E29" s="60" t="n"/>
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
@@ -3196,10 +3058,7 @@
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="59" t="n"/>
       <c r="D30" s="59" t="n"/>
-      <c r="E30" s="60">
-        <f>IF(OR(N(C30)=0,N(D30)=0),"",C30*D30)</f>
-        <v/>
-      </c>
+      <c r="E30" s="60" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="24" t="inlineStr">
         <is>
@@ -3221,10 +3080,7 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="59" t="n"/>
       <c r="D31" s="59" t="n"/>
-      <c r="E31" s="60">
-        <f>IF(OR(N(C31)=0,N(D31)=0),"",C31*D31)</f>
-        <v/>
-      </c>
+      <c r="E31" s="60" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="24" t="inlineStr">
         <is>
@@ -3246,10 +3102,7 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="59" t="n"/>
       <c r="D32" s="59" t="n"/>
-      <c r="E32" s="60">
-        <f>IF(OR(N(C32)=0,N(D32)=0),"",C32*D32)</f>
-        <v/>
-      </c>
+      <c r="E32" s="60" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="24" t="inlineStr">
         <is>
@@ -3271,10 +3124,7 @@
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="59" t="n"/>
       <c r="D33" s="59" t="n"/>
-      <c r="E33" s="60">
-        <f>IF(OR(N(C33)=0,N(D33)=0),"",C33*D33)</f>
-        <v/>
-      </c>
+      <c r="E33" s="60" t="n"/>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="24" t="inlineStr">
         <is>
@@ -3296,10 +3146,7 @@
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="59" t="n"/>
       <c r="D34" s="59" t="n"/>
-      <c r="E34" s="60">
-        <f>IF(OR(N(C34)=0,N(D34)=0),"",C34*D34)</f>
-        <v/>
-      </c>
+      <c r="E34" s="60" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="24" t="inlineStr">
         <is>
@@ -3317,10 +3164,7 @@
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="59" t="n"/>
       <c r="D35" s="59" t="n"/>
-      <c r="E35" s="60">
-        <f>IF(OR(N(C35)=0,N(D35)=0),"",C35*D35)</f>
-        <v/>
-      </c>
+      <c r="E35" s="60" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="6" t="n"/>
@@ -3334,10 +3178,7 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="59" t="n"/>
       <c r="D36" s="59" t="n"/>
-      <c r="E36" s="60">
-        <f>IF(OR(N(C36)=0,N(D36)=0),"",C36*D36)</f>
-        <v/>
-      </c>
+      <c r="E36" s="60" t="n"/>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="24" t="n"/>
       <c r="H36" s="6" t="n"/>
@@ -3355,10 +3196,7 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="61">
-        <f>IF(SUM(E26:E36)=0,"",SUM(E26:E36))</f>
-        <v/>
-      </c>
+      <c r="E37" s="61" t="n"/>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="25" t="inlineStr"/>
       <c r="H37" s="6" t="n"/>
@@ -4418,14 +4256,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F59E0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.6" customWidth="1" min="1" max="1"/>
@@ -4448,89 +4285,154 @@
           <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="130" customHeight="1"/>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>하 수 관 거   시 공 계 획 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1"/>
-    <row r="5" ht="30" customHeight="1">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1"/>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>목          차</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>가나지구 하수관로 정비공사</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>공 사 개 요</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>제 출 일</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="n">
-        <v>46106</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="200" customHeight="1"/>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 사람).</t>
-        </is>
-      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>위  치  도</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>현 장 조 직 도</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>예 정 공 정 표</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>주요 공정의 시공절차 및 방법</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>일일 시공 일정</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>주요 장비 및 인력 투입 계획</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>안전 및 환경관리 계획</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="19">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="D8:K8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
@@ -4538,10 +4440,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F59E0B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4568,9 +4469,9 @@
           <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -4589,10 +4490,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="14">
-        <f>IF('예시-표지'!E5="","",'예시-표지'!E5)</f>
-        <v/>
-      </c>
+      <c r="C4" s="14" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
@@ -4610,9 +4508,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="15" t="n">
-        <v>2480000000</v>
-      </c>
+      <c r="C5" s="15" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
@@ -4622,11 +4518,7 @@
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>가나시</t>
-        </is>
-      </c>
+      <c r="I5" s="16" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
@@ -4638,11 +4530,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>가나시 가나면 가나리 일원</t>
-        </is>
-      </c>
+      <c r="C6" s="16" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
@@ -4652,11 +4540,7 @@
         </is>
       </c>
       <c r="H6" s="6" t="n"/>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>총액입찰</t>
-        </is>
-      </c>
+      <c r="I6" s="16" t="n"/>
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
@@ -4668,11 +4552,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>가나시 하수도과</t>
-        </is>
-      </c>
+      <c r="C7" s="16" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
@@ -4682,21 +4562,14 @@
         </is>
       </c>
       <c r="H7" s="6" t="n"/>
-      <c r="I7" s="17" t="n">
-        <v>46113</v>
-      </c>
+      <c r="I7" s="17" t="n"/>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>46466</v>
-      </c>
+      <c r="K7" s="18" t="n"/>
       <c r="L7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr"/>
-      <c r="I8" s="19">
-        <f>IF(OR(N(I7)=0,N(K7)=0),"",IF(K7&lt;I7,"⚠ 준공일이 착공일보다 빠름",K7-I7+1))</f>
-        <v/>
-      </c>
+      <c r="I8" s="19" t="n"/>
     </row>
     <row r="9" ht="6" customHeight="1"/>
     <row r="10" ht="3" customHeight="1"/>
@@ -4749,11 +4622,7 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>D200mm 내충격 PVC</t>
-        </is>
-      </c>
+      <c r="D13" s="22" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
@@ -4762,9 +4631,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="I13" s="23" t="n">
-        <v>3250</v>
-      </c>
+      <c r="I13" s="23" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="24" t="n"/>
       <c r="L13" s="6" t="n"/>
@@ -4777,11 +4644,7 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>D250mm 내충격 PVC</t>
-        </is>
-      </c>
+      <c r="D14" s="22" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
@@ -4790,9 +4653,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="I14" s="23" t="n">
-        <v>1180</v>
-      </c>
+      <c r="I14" s="23" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="24" t="n"/>
       <c r="L14" s="6" t="n"/>
@@ -4805,11 +4666,7 @@
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>D300mm 내충격 PVC</t>
-        </is>
-      </c>
+      <c r="D15" s="22" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
@@ -4818,9 +4675,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="I15" s="23" t="n">
-        <v>420</v>
-      </c>
+      <c r="I15" s="23" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="24" t="n"/>
       <c r="L15" s="6" t="n"/>
@@ -4833,11 +4688,7 @@
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>원형 1호(D900)</t>
-        </is>
-      </c>
+      <c r="D16" s="22" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
@@ -4846,9 +4697,7 @@
           <t>개소</t>
         </is>
       </c>
-      <c r="I16" s="23" t="n">
-        <v>186</v>
-      </c>
+      <c r="I16" s="23" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="24" t="n"/>
       <c r="L16" s="6" t="n"/>
@@ -4861,11 +4710,7 @@
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>PVC 오수받이 D300</t>
-        </is>
-      </c>
+      <c r="D17" s="22" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
@@ -4874,15 +4719,9 @@
           <t>가구</t>
         </is>
       </c>
-      <c r="I17" s="23" t="n">
-        <v>412</v>
-      </c>
+      <c r="I17" s="23" t="n"/>
       <c r="J17" s="6" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>연결관 포함</t>
-        </is>
-      </c>
+      <c r="K17" s="24" t="n"/>
       <c r="L17" s="6" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -4893,11 +4732,7 @@
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>소형</t>
-        </is>
-      </c>
+      <c r="D18" s="22" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
@@ -4906,9 +4741,7 @@
           <t>개소</t>
         </is>
       </c>
-      <c r="I18" s="23" t="n">
-        <v>2</v>
-      </c>
+      <c r="I18" s="23" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="24" t="n"/>
       <c r="L18" s="6" t="n"/>
@@ -4954,10 +4787,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
-      <c r="I21" s="26">
-        <f>IF(SUMIF(H13:H20,"m",I13:I20)=0,"",SUMIF(H13:H20,"m",I13:I20))</f>
-        <v/>
-      </c>
+      <c r="I21" s="26" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="25" t="inlineStr"/>
       <c r="L21" s="6" t="n"/>
@@ -4972,10 +4802,7 @@
       </c>
     </row>
     <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="27">
-        <f>"    "&amp;IF(C6="","대상 지역",C6)&amp;"의 합류식 하수관로를 분류식으로 바꾸고 하수관로를 체계적으로 정비하여 마을에서 생기는 오수를 모두 차집 · 처리함으로써, 하수처리 효율을 높이고 위생적인 생활환경을 만들며 방류 수역의 수질을 지키는 데 목적이 있습니다."</f>
-        <v/>
-      </c>
+      <c r="A25" s="27" t="n"/>
     </row>
     <row r="26" ht="3" customHeight="1"/>
     <row r="27" ht="21" customHeight="1">
@@ -4986,11 +4813,7 @@
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>면 소재지를 지나는 도로 구간이 많아 당일 굴착 · 당일 복구를 원칙으로 함</t>
-        </is>
-      </c>
+      <c r="A28" s="28" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
@@ -5003,8 +4826,13 @@
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="10" t="inlineStr"/>
+    <row r="29"/>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>하늘색 칸 = 자동(공사명 · 공사 일수 · 관로 연장 합계 · 목적 글).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="65">
@@ -5074,3626 +4902,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="I5:L5"/>
   </mergeCells>
-  <conditionalFormatting sqref="I13:I20">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(I13),MOD(I13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(ISNUMBER(I21),MOD(I21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>2.  위  치  도</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>(위치도를 붙이는 곳 — 현장 위치 · 공사 구간을 표시한 지도)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="10" customHeight="1"/>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>3.  현 장 조 직 도</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1">
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>현 장 소 장</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="F24" s="30" t="inlineStr">
-        <is>
-          <t>010-0000-0001</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="G25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>안 전 담 당</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="G27" s="31" t="n"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="G28" s="31" t="n"/>
-      <c r="I28" s="30" t="inlineStr">
-        <is>
-          <t>010-0000-0002</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="G29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1">
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="33" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="D31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>공 사 과 장</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>공 사 대 리</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>이과장</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>박대리</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="C34" s="30" t="inlineStr">
-        <is>
-          <t>010-0000-0003</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="I34" s="30" t="inlineStr">
-        <is>
-          <t>010-0000-0004</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="J35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>작 업 반 장</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>최반장</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="I38" s="30" t="inlineStr">
-        <is>
-          <t>010-0000-0005</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="n"/>
-    </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>※ 칸마다 성명 · 연락처를 적습니다. 안전담당은 현장소장 직속으로 둡니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:L17"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AC19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="2.3" customWidth="1" min="5" max="5"/>
-    <col width="2.3" customWidth="1" min="6" max="6"/>
-    <col width="2.3" customWidth="1" min="7" max="7"/>
-    <col width="2.3" customWidth="1" min="8" max="8"/>
-    <col width="2.3" customWidth="1" min="9" max="9"/>
-    <col width="2.3" customWidth="1" min="10" max="10"/>
-    <col width="2.3" customWidth="1" min="11" max="11"/>
-    <col width="2.3" customWidth="1" min="12" max="12"/>
-    <col width="2.3" customWidth="1" min="13" max="13"/>
-    <col width="2.3" customWidth="1" min="14" max="14"/>
-    <col width="2.3" customWidth="1" min="15" max="15"/>
-    <col width="2.3" customWidth="1" min="16" max="16"/>
-    <col width="2.3" customWidth="1" min="17" max="17"/>
-    <col width="2.3" customWidth="1" min="18" max="18"/>
-    <col width="2.3" customWidth="1" min="19" max="19"/>
-    <col width="2.3" customWidth="1" min="20" max="20"/>
-    <col width="2.3" customWidth="1" min="21" max="21"/>
-    <col width="2.3" customWidth="1" min="22" max="22"/>
-    <col width="2.3" customWidth="1" min="23" max="23"/>
-    <col width="2.3" customWidth="1" min="24" max="24"/>
-    <col width="2.3" customWidth="1" min="25" max="25"/>
-    <col width="2.3" customWidth="1" min="26" max="26"/>
-    <col width="2.3" customWidth="1" min="27" max="27"/>
-    <col width="2.3" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="I1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>4.  예 정 공 정 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>착 공 일</t>
-        </is>
-      </c>
-      <c r="B3" s="35">
-        <f>IF(N('예시-1.공사개요'!I7)=0,"",'예시-1.공사개요'!I7)</f>
-        <v/>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>※ 착공일은 1. 공사개요에서 따라옵니다. 공종마다 착수 · 완료일을 적으면 막대가 그려집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>공    종</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>착 수</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>완 료</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>일 수</t>
-        </is>
-      </c>
-      <c r="E4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n"/>
-      <c r="S4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="T4" s="6" t="n"/>
-      <c r="U4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="V4" s="6" t="n"/>
-      <c r="W4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="X4" s="6" t="n"/>
-      <c r="Y4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="6" t="n"/>
-      <c r="AA4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AB4" s="6" t="n"/>
-      <c r="AC4" s="21" t="inlineStr">
-        <is>
-          <t>비 고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="G5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="H5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="J5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="K5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="L5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="M5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="O5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="P5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="Q5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="R5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="S5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="T5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="U5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="V5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="W5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="X5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="Y5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="Z5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="AA5" s="37" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB5" s="37" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="AC5" s="6" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="12" customHeight="1">
-      <c r="E6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+15)</f>
-        <v/>
-      </c>
-      <c r="G6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="H6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+15)</f>
-        <v/>
-      </c>
-      <c r="I6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="J6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+15)</f>
-        <v/>
-      </c>
-      <c r="K6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="L6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+15)</f>
-        <v/>
-      </c>
-      <c r="M6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="N6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+15)</f>
-        <v/>
-      </c>
-      <c r="O6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="P6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+15)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="R6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+15)</f>
-        <v/>
-      </c>
-      <c r="S6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="T6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+15)</f>
-        <v/>
-      </c>
-      <c r="U6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="V6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+15)</f>
-        <v/>
-      </c>
-      <c r="W6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="X6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+15)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+15)</f>
-        <v/>
-      </c>
-      <c r="AA6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" hidden="1" ht="12" customHeight="1">
-      <c r="E7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+14)</f>
-        <v/>
-      </c>
-      <c r="F7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)-1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+14)</f>
-        <v/>
-      </c>
-      <c r="H7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)-1)</f>
-        <v/>
-      </c>
-      <c r="I7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+14)</f>
-        <v/>
-      </c>
-      <c r="J7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)-1)</f>
-        <v/>
-      </c>
-      <c r="K7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+14)</f>
-        <v/>
-      </c>
-      <c r="L7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)-1)</f>
-        <v/>
-      </c>
-      <c r="M7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+14)</f>
-        <v/>
-      </c>
-      <c r="N7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)-1)</f>
-        <v/>
-      </c>
-      <c r="O7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+14)</f>
-        <v/>
-      </c>
-      <c r="P7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)-1)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+14)</f>
-        <v/>
-      </c>
-      <c r="R7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)-1)</f>
-        <v/>
-      </c>
-      <c r="S7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+14)</f>
-        <v/>
-      </c>
-      <c r="T7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)-1)</f>
-        <v/>
-      </c>
-      <c r="U7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+14)</f>
-        <v/>
-      </c>
-      <c r="V7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)-1)</f>
-        <v/>
-      </c>
-      <c r="W7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+14)</f>
-        <v/>
-      </c>
-      <c r="X7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)-1)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+14)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)-1)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+14)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),12)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>준비공(측량 · 지장물 조사)</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C8" s="39" t="n">
-        <v>46142</v>
-      </c>
-      <c r="D8" s="40">
-        <f>IF(OR(N(B8)=0,N(C8)=0),"",IF(C8&lt;B8,"⚠",C8-B8+1))</f>
-        <v/>
-      </c>
-      <c r="E8" s="41" t="inlineStr"/>
-      <c r="F8" s="41" t="inlineStr"/>
-      <c r="G8" s="41" t="inlineStr"/>
-      <c r="H8" s="41" t="inlineStr"/>
-      <c r="I8" s="41" t="inlineStr"/>
-      <c r="J8" s="41" t="inlineStr"/>
-      <c r="K8" s="41" t="inlineStr"/>
-      <c r="L8" s="41" t="inlineStr"/>
-      <c r="M8" s="41" t="inlineStr"/>
-      <c r="N8" s="41" t="inlineStr"/>
-      <c r="O8" s="41" t="inlineStr"/>
-      <c r="P8" s="41" t="inlineStr"/>
-      <c r="Q8" s="41" t="inlineStr"/>
-      <c r="R8" s="41" t="inlineStr"/>
-      <c r="S8" s="41" t="inlineStr"/>
-      <c r="T8" s="41" t="inlineStr"/>
-      <c r="U8" s="41" t="inlineStr"/>
-      <c r="V8" s="41" t="inlineStr"/>
-      <c r="W8" s="41" t="inlineStr"/>
-      <c r="X8" s="41" t="inlineStr"/>
-      <c r="Y8" s="41" t="inlineStr"/>
-      <c r="Z8" s="41" t="inlineStr"/>
-      <c r="AA8" s="41" t="inlineStr"/>
-      <c r="AB8" s="41" t="inlineStr"/>
-      <c r="AC8" s="42" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>관로 터파기 · 가시설</t>
-        </is>
-      </c>
-      <c r="B9" s="39" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C9" s="39" t="n">
-        <v>46341</v>
-      </c>
-      <c r="D9" s="40">
-        <f>IF(OR(N(B9)=0,N(C9)=0),"",IF(C9&lt;B9,"⚠",C9-B9+1))</f>
-        <v/>
-      </c>
-      <c r="E9" s="41" t="inlineStr"/>
-      <c r="F9" s="41" t="inlineStr"/>
-      <c r="G9" s="41" t="inlineStr"/>
-      <c r="H9" s="41" t="inlineStr"/>
-      <c r="I9" s="41" t="inlineStr"/>
-      <c r="J9" s="41" t="inlineStr"/>
-      <c r="K9" s="41" t="inlineStr"/>
-      <c r="L9" s="41" t="inlineStr"/>
-      <c r="M9" s="41" t="inlineStr"/>
-      <c r="N9" s="41" t="inlineStr"/>
-      <c r="O9" s="41" t="inlineStr"/>
-      <c r="P9" s="41" t="inlineStr"/>
-      <c r="Q9" s="41" t="inlineStr"/>
-      <c r="R9" s="41" t="inlineStr"/>
-      <c r="S9" s="41" t="inlineStr"/>
-      <c r="T9" s="41" t="inlineStr"/>
-      <c r="U9" s="41" t="inlineStr"/>
-      <c r="V9" s="41" t="inlineStr"/>
-      <c r="W9" s="41" t="inlineStr"/>
-      <c r="X9" s="41" t="inlineStr"/>
-      <c r="Y9" s="41" t="inlineStr"/>
-      <c r="Z9" s="41" t="inlineStr"/>
-      <c r="AA9" s="41" t="inlineStr"/>
-      <c r="AB9" s="41" t="inlineStr"/>
-      <c r="AC9" s="42" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>관 부설 및 접합</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="n">
-        <v>46148</v>
-      </c>
-      <c r="C10" s="39" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D10" s="40">
-        <f>IF(OR(N(B10)=0,N(C10)=0),"",IF(C10&lt;B10,"⚠",C10-B10+1))</f>
-        <v/>
-      </c>
-      <c r="E10" s="41" t="inlineStr"/>
-      <c r="F10" s="41" t="inlineStr"/>
-      <c r="G10" s="41" t="inlineStr"/>
-      <c r="H10" s="41" t="inlineStr"/>
-      <c r="I10" s="41" t="inlineStr"/>
-      <c r="J10" s="41" t="inlineStr"/>
-      <c r="K10" s="41" t="inlineStr"/>
-      <c r="L10" s="41" t="inlineStr"/>
-      <c r="M10" s="41" t="inlineStr"/>
-      <c r="N10" s="41" t="inlineStr"/>
-      <c r="O10" s="41" t="inlineStr"/>
-      <c r="P10" s="41" t="inlineStr"/>
-      <c r="Q10" s="41" t="inlineStr"/>
-      <c r="R10" s="41" t="inlineStr"/>
-      <c r="S10" s="41" t="inlineStr"/>
-      <c r="T10" s="41" t="inlineStr"/>
-      <c r="U10" s="41" t="inlineStr"/>
-      <c r="V10" s="41" t="inlineStr"/>
-      <c r="W10" s="41" t="inlineStr"/>
-      <c r="X10" s="41" t="inlineStr"/>
-      <c r="Y10" s="41" t="inlineStr"/>
-      <c r="Z10" s="41" t="inlineStr"/>
-      <c r="AA10" s="41" t="inlineStr"/>
-      <c r="AB10" s="41" t="inlineStr"/>
-      <c r="AC10" s="42" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>맨홀 설치</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="n">
-        <v>46153</v>
-      </c>
-      <c r="C11" s="39" t="n">
-        <v>46351</v>
-      </c>
-      <c r="D11" s="40">
-        <f>IF(OR(N(B11)=0,N(C11)=0),"",IF(C11&lt;B11,"⚠",C11-B11+1))</f>
-        <v/>
-      </c>
-      <c r="E11" s="41" t="inlineStr"/>
-      <c r="F11" s="41" t="inlineStr"/>
-      <c r="G11" s="41" t="inlineStr"/>
-      <c r="H11" s="41" t="inlineStr"/>
-      <c r="I11" s="41" t="inlineStr"/>
-      <c r="J11" s="41" t="inlineStr"/>
-      <c r="K11" s="41" t="inlineStr"/>
-      <c r="L11" s="41" t="inlineStr"/>
-      <c r="M11" s="41" t="inlineStr"/>
-      <c r="N11" s="41" t="inlineStr"/>
-      <c r="O11" s="41" t="inlineStr"/>
-      <c r="P11" s="41" t="inlineStr"/>
-      <c r="Q11" s="41" t="inlineStr"/>
-      <c r="R11" s="41" t="inlineStr"/>
-      <c r="S11" s="41" t="inlineStr"/>
-      <c r="T11" s="41" t="inlineStr"/>
-      <c r="U11" s="41" t="inlineStr"/>
-      <c r="V11" s="41" t="inlineStr"/>
-      <c r="W11" s="41" t="inlineStr"/>
-      <c r="X11" s="41" t="inlineStr"/>
-      <c r="Y11" s="41" t="inlineStr"/>
-      <c r="Z11" s="41" t="inlineStr"/>
-      <c r="AA11" s="41" t="inlineStr"/>
-      <c r="AB11" s="41" t="inlineStr"/>
-      <c r="AC11" s="42" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>되메우기 · 다짐 · 가복구</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="n">
-        <v>46148</v>
-      </c>
-      <c r="C12" s="39" t="n">
-        <v>46356</v>
-      </c>
-      <c r="D12" s="40">
-        <f>IF(OR(N(B12)=0,N(C12)=0),"",IF(C12&lt;B12,"⚠",C12-B12+1))</f>
-        <v/>
-      </c>
-      <c r="E12" s="41" t="inlineStr"/>
-      <c r="F12" s="41" t="inlineStr"/>
-      <c r="G12" s="41" t="inlineStr"/>
-      <c r="H12" s="41" t="inlineStr"/>
-      <c r="I12" s="41" t="inlineStr"/>
-      <c r="J12" s="41" t="inlineStr"/>
-      <c r="K12" s="41" t="inlineStr"/>
-      <c r="L12" s="41" t="inlineStr"/>
-      <c r="M12" s="41" t="inlineStr"/>
-      <c r="N12" s="41" t="inlineStr"/>
-      <c r="O12" s="41" t="inlineStr"/>
-      <c r="P12" s="41" t="inlineStr"/>
-      <c r="Q12" s="41" t="inlineStr"/>
-      <c r="R12" s="41" t="inlineStr"/>
-      <c r="S12" s="41" t="inlineStr"/>
-      <c r="T12" s="41" t="inlineStr"/>
-      <c r="U12" s="41" t="inlineStr"/>
-      <c r="V12" s="41" t="inlineStr"/>
-      <c r="W12" s="41" t="inlineStr"/>
-      <c r="X12" s="41" t="inlineStr"/>
-      <c r="Y12" s="41" t="inlineStr"/>
-      <c r="Z12" s="41" t="inlineStr"/>
-      <c r="AA12" s="41" t="inlineStr"/>
-      <c r="AB12" s="41" t="inlineStr"/>
-      <c r="AC12" s="42" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>배수설비(오수받이 · 연결관)</t>
-        </is>
-      </c>
-      <c r="B13" s="39" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>46418</v>
-      </c>
-      <c r="D13" s="40">
-        <f>IF(OR(N(B13)=0,N(C13)=0),"",IF(C13&lt;B13,"⚠",C13-B13+1))</f>
-        <v/>
-      </c>
-      <c r="E13" s="41" t="inlineStr"/>
-      <c r="F13" s="41" t="inlineStr"/>
-      <c r="G13" s="41" t="inlineStr"/>
-      <c r="H13" s="41" t="inlineStr"/>
-      <c r="I13" s="41" t="inlineStr"/>
-      <c r="J13" s="41" t="inlineStr"/>
-      <c r="K13" s="41" t="inlineStr"/>
-      <c r="L13" s="41" t="inlineStr"/>
-      <c r="M13" s="41" t="inlineStr"/>
-      <c r="N13" s="41" t="inlineStr"/>
-      <c r="O13" s="41" t="inlineStr"/>
-      <c r="P13" s="41" t="inlineStr"/>
-      <c r="Q13" s="41" t="inlineStr"/>
-      <c r="R13" s="41" t="inlineStr"/>
-      <c r="S13" s="41" t="inlineStr"/>
-      <c r="T13" s="41" t="inlineStr"/>
-      <c r="U13" s="41" t="inlineStr"/>
-      <c r="V13" s="41" t="inlineStr"/>
-      <c r="W13" s="41" t="inlineStr"/>
-      <c r="X13" s="41" t="inlineStr"/>
-      <c r="Y13" s="41" t="inlineStr"/>
-      <c r="Z13" s="41" t="inlineStr"/>
-      <c r="AA13" s="41" t="inlineStr"/>
-      <c r="AB13" s="41" t="inlineStr"/>
-      <c r="AC13" s="42" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>수밀 · CCTV · 연막 검사</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C14" s="39" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D14" s="40">
-        <f>IF(OR(N(B14)=0,N(C14)=0),"",IF(C14&lt;B14,"⚠",C14-B14+1))</f>
-        <v/>
-      </c>
-      <c r="E14" s="41" t="inlineStr"/>
-      <c r="F14" s="41" t="inlineStr"/>
-      <c r="G14" s="41" t="inlineStr"/>
-      <c r="H14" s="41" t="inlineStr"/>
-      <c r="I14" s="41" t="inlineStr"/>
-      <c r="J14" s="41" t="inlineStr"/>
-      <c r="K14" s="41" t="inlineStr"/>
-      <c r="L14" s="41" t="inlineStr"/>
-      <c r="M14" s="41" t="inlineStr"/>
-      <c r="N14" s="41" t="inlineStr"/>
-      <c r="O14" s="41" t="inlineStr"/>
-      <c r="P14" s="41" t="inlineStr"/>
-      <c r="Q14" s="41" t="inlineStr"/>
-      <c r="R14" s="41" t="inlineStr"/>
-      <c r="S14" s="41" t="inlineStr"/>
-      <c r="T14" s="41" t="inlineStr"/>
-      <c r="U14" s="41" t="inlineStr"/>
-      <c r="V14" s="41" t="inlineStr"/>
-      <c r="W14" s="41" t="inlineStr"/>
-      <c r="X14" s="41" t="inlineStr"/>
-      <c r="Y14" s="41" t="inlineStr"/>
-      <c r="Z14" s="41" t="inlineStr"/>
-      <c r="AA14" s="41" t="inlineStr"/>
-      <c r="AB14" s="41" t="inlineStr"/>
-      <c r="AC14" s="42" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>포장 본복구</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>46446</v>
-      </c>
-      <c r="D15" s="40">
-        <f>IF(OR(N(B15)=0,N(C15)=0),"",IF(C15&lt;B15,"⚠",C15-B15+1))</f>
-        <v/>
-      </c>
-      <c r="E15" s="41" t="inlineStr"/>
-      <c r="F15" s="41" t="inlineStr"/>
-      <c r="G15" s="41" t="inlineStr"/>
-      <c r="H15" s="41" t="inlineStr"/>
-      <c r="I15" s="41" t="inlineStr"/>
-      <c r="J15" s="41" t="inlineStr"/>
-      <c r="K15" s="41" t="inlineStr"/>
-      <c r="L15" s="41" t="inlineStr"/>
-      <c r="M15" s="41" t="inlineStr"/>
-      <c r="N15" s="41" t="inlineStr"/>
-      <c r="O15" s="41" t="inlineStr"/>
-      <c r="P15" s="41" t="inlineStr"/>
-      <c r="Q15" s="41" t="inlineStr"/>
-      <c r="R15" s="41" t="inlineStr"/>
-      <c r="S15" s="41" t="inlineStr"/>
-      <c r="T15" s="41" t="inlineStr"/>
-      <c r="U15" s="41" t="inlineStr"/>
-      <c r="V15" s="41" t="inlineStr"/>
-      <c r="W15" s="41" t="inlineStr"/>
-      <c r="X15" s="41" t="inlineStr"/>
-      <c r="Y15" s="41" t="inlineStr"/>
-      <c r="Z15" s="41" t="inlineStr"/>
-      <c r="AA15" s="41" t="inlineStr"/>
-      <c r="AB15" s="41" t="inlineStr"/>
-      <c r="AC15" s="42" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>정리 및 준공</t>
-        </is>
-      </c>
-      <c r="B16" s="39" t="n">
-        <v>46447</v>
-      </c>
-      <c r="C16" s="39" t="n">
-        <v>46466</v>
-      </c>
-      <c r="D16" s="40">
-        <f>IF(OR(N(B16)=0,N(C16)=0),"",IF(C16&lt;B16,"⚠",C16-B16+1))</f>
-        <v/>
-      </c>
-      <c r="E16" s="41" t="inlineStr"/>
-      <c r="F16" s="41" t="inlineStr"/>
-      <c r="G16" s="41" t="inlineStr"/>
-      <c r="H16" s="41" t="inlineStr"/>
-      <c r="I16" s="41" t="inlineStr"/>
-      <c r="J16" s="41" t="inlineStr"/>
-      <c r="K16" s="41" t="inlineStr"/>
-      <c r="L16" s="41" t="inlineStr"/>
-      <c r="M16" s="41" t="inlineStr"/>
-      <c r="N16" s="41" t="inlineStr"/>
-      <c r="O16" s="41" t="inlineStr"/>
-      <c r="P16" s="41" t="inlineStr"/>
-      <c r="Q16" s="41" t="inlineStr"/>
-      <c r="R16" s="41" t="inlineStr"/>
-      <c r="S16" s="41" t="inlineStr"/>
-      <c r="T16" s="41" t="inlineStr"/>
-      <c r="U16" s="41" t="inlineStr"/>
-      <c r="V16" s="41" t="inlineStr"/>
-      <c r="W16" s="41" t="inlineStr"/>
-      <c r="X16" s="41" t="inlineStr"/>
-      <c r="Y16" s="41" t="inlineStr"/>
-      <c r="Z16" s="41" t="inlineStr"/>
-      <c r="AA16" s="41" t="inlineStr"/>
-      <c r="AB16" s="41" t="inlineStr"/>
-      <c r="AC16" s="42" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="39" t="n"/>
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="40">
-        <f>IF(OR(N(B17)=0,N(C17)=0),"",IF(C17&lt;B17,"⚠",C17-B17+1))</f>
-        <v/>
-      </c>
-      <c r="E17" s="41" t="inlineStr"/>
-      <c r="F17" s="41" t="inlineStr"/>
-      <c r="G17" s="41" t="inlineStr"/>
-      <c r="H17" s="41" t="inlineStr"/>
-      <c r="I17" s="41" t="inlineStr"/>
-      <c r="J17" s="41" t="inlineStr"/>
-      <c r="K17" s="41" t="inlineStr"/>
-      <c r="L17" s="41" t="inlineStr"/>
-      <c r="M17" s="41" t="inlineStr"/>
-      <c r="N17" s="41" t="inlineStr"/>
-      <c r="O17" s="41" t="inlineStr"/>
-      <c r="P17" s="41" t="inlineStr"/>
-      <c r="Q17" s="41" t="inlineStr"/>
-      <c r="R17" s="41" t="inlineStr"/>
-      <c r="S17" s="41" t="inlineStr"/>
-      <c r="T17" s="41" t="inlineStr"/>
-      <c r="U17" s="41" t="inlineStr"/>
-      <c r="V17" s="41" t="inlineStr"/>
-      <c r="W17" s="41" t="inlineStr"/>
-      <c r="X17" s="41" t="inlineStr"/>
-      <c r="Y17" s="41" t="inlineStr"/>
-      <c r="Z17" s="41" t="inlineStr"/>
-      <c r="AA17" s="41" t="inlineStr"/>
-      <c r="AB17" s="41" t="inlineStr"/>
-      <c r="AC17" s="42" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="39" t="n"/>
-      <c r="C18" s="39" t="n"/>
-      <c r="D18" s="40">
-        <f>IF(OR(N(B18)=0,N(C18)=0),"",IF(C18&lt;B18,"⚠",C18-B18+1))</f>
-        <v/>
-      </c>
-      <c r="E18" s="41" t="inlineStr"/>
-      <c r="F18" s="41" t="inlineStr"/>
-      <c r="G18" s="41" t="inlineStr"/>
-      <c r="H18" s="41" t="inlineStr"/>
-      <c r="I18" s="41" t="inlineStr"/>
-      <c r="J18" s="41" t="inlineStr"/>
-      <c r="K18" s="41" t="inlineStr"/>
-      <c r="L18" s="41" t="inlineStr"/>
-      <c r="M18" s="41" t="inlineStr"/>
-      <c r="N18" s="41" t="inlineStr"/>
-      <c r="O18" s="41" t="inlineStr"/>
-      <c r="P18" s="41" t="inlineStr"/>
-      <c r="Q18" s="41" t="inlineStr"/>
-      <c r="R18" s="41" t="inlineStr"/>
-      <c r="S18" s="41" t="inlineStr"/>
-      <c r="T18" s="41" t="inlineStr"/>
-      <c r="U18" s="41" t="inlineStr"/>
-      <c r="V18" s="41" t="inlineStr"/>
-      <c r="W18" s="41" t="inlineStr"/>
-      <c r="X18" s="41" t="inlineStr"/>
-      <c r="Y18" s="41" t="inlineStr"/>
-      <c r="Z18" s="41" t="inlineStr"/>
-      <c r="AA18" s="41" t="inlineStr"/>
-      <c r="AB18" s="41" t="inlineStr"/>
-      <c r="AC18" s="42" t="n"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>※ 일수 = 완료 − 착수 + 1. 공정은 현장 여건 · 민원 · 날씨에 따라 바뀔 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="A19:AC19"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="I1:AC1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A2:AC2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D3:AC3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E8:AB18">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(N($B8)&gt;0,N($C8)&gt;=N($B8),$B8&lt;=E$7,$C8&gt;=E$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>6.  일일 시공 일정</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="52.5" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
-        <is>
-          <t>본 공사는 마을 안 도로를 지나는 작업이 많으므로, 하루 작업량은 관을 묻고 되메우기까지 끝내 보행자 · 차량 통행에 지장이 없게 정합니다. 휴식 · 점심 시간에 생길 수 있는 안전사고에 주의하고, 공사로 생긴 잡자재 · 쓰레기는 작업이 끝나기 전에 치웁니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="4" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>시  작</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>끝</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>소요 시간</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>작 업 내 용</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="52" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="52" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="53">
-        <f>IF(OR(A7="",C7=""),"",IF(C7&lt;A7,"⚠",ROUND((C7-A7)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>TBM(작업 전 안전점검 회의) · 안전교육 · 건강 상태 확인</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="52" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="52" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="53">
-        <f>IF(OR(A8="",C8=""),"",IF(C8&lt;A8,"⚠",ROUND((C8-A8)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>장비 점검 · 교통 안전시설 설치</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="52" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="52" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="53">
-        <f>IF(OR(A9="",C9=""),"",IF(C9&lt;A9,"⚠",ROUND((C9-A9)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t>포장 절단 · 깨기</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="52" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="53">
-        <f>IF(OR(A10="",C10=""),"",IF(C10&lt;A10,"⚠",ROUND((C10-A10)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>터파기 · 가시설 · 관 부설 및 접합</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="52" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="53">
-        <f>IF(OR(A11="",C11=""),"",IF(C11&lt;A11,"⚠",ROUND((C11-A11)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>점심 · 휴식(개착 구간 안전시설 확인)</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="52" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="52" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="53">
-        <f>IF(OR(A12="",C12=""),"",IF(C12&lt;A12,"⚠",ROUND((C12-A12)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>관 부설 · 맨홀 · 되메우기</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="52" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="52" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="53">
-        <f>IF(OR(A13="",C13=""),"",IF(C13&lt;A13,"⚠",ROUND((C13-A13)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>휴식</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="52" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="52" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="53">
-        <f>IF(OR(A14="",C14=""),"",IF(C14&lt;A14,"⚠",ROUND((C14-A14)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>되메우기 다짐 · 가복구</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="52" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="52" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="53">
-        <f>IF(OR(A15="",C15=""),"",IF(C15&lt;A15,"⚠",ROUND((C15-A15)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t>현장 정리 · 청소 · 잔재 반출</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="52" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="53">
-        <f>IF(OR(A16="",C16=""),"",IF(C16&lt;A16,"⚠",ROUND((C16-A16)*24*60,0)))</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>하루 작업 시간 (처음 시작 ~ 마지막 끝)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="54">
-        <f>IF(OR(COUNT(A7:A16)=0,COUNT(C7:C16)=0),"",ROUND((MAX(C7:C16)-MIN(A7:A16))*24,2))</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="25" t="inlineStr"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="10" customHeight="1"/>
-    <row r="19" ht="3" customHeight="1"/>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>관로 부설 소요 일수 (어림)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>관로 연장 합계</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="55">
-        <f>IF(N('예시-1.공사개요'!I21)=0,"",'예시-1.공사개요'!I21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>1조 하루 부설량</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="56" t="n">
-        <v>25</v>
-      </c>
-      <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>작업 조 수</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>부설 소요 일수</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="58">
-        <f>IF(OR(N(E21)=0,N(K21)=0,N(E22)=0),"",ROUNDUP(E21/(K21*E22),0))</f>
-        <v/>
-      </c>
-      <c r="L22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>※ 부설 소요 일수 = 관로 연장 ÷ (하루 부설량 × 조 수), 올림. 하루 부설량(노란 칸)은 관경 · 깊이 · 포장 · 민원 여건에 맞게 적습니다. 배관 1조의 하루 터파기는 그날 부설할 연장을 넘지 않게 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G7:L7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(ISNUMBER(E21),MOD(E21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K21">
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(ISNUMBER(K21),MOD(K21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>7.  주요 장비 및 인력 투입 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="3" customHeight="1"/>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>1) 장비 투입 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>장 비 명</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>규  격</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>1일
-(대)</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>투입
-일수</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>누  계
-(대·일)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>작 업 내 용</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>굴삭기</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>0.6㎥</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G7" s="60">
-        <f>IF(OR(N(E7)=0,N(F7)=0),"",E7*F7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>포장 깨기 · 터파기 · 가시설 설치</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>굴삭기</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>0.3㎥</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="59" t="n">
-        <v>180</v>
-      </c>
-      <c r="G8" s="60">
-        <f>IF(OR(N(E8)=0,N(F8)=0),"",E8*F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>포장 깨기 · 터파기 · 되메우기</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>굴삭기</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>0.15㎥</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="G9" s="60">
-        <f>IF(OR(N(E9)=0,N(F9)=0),"",E9*F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>지선 관로 터파기 · 되메우기</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>다짐장비</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>진동롤러 1.0톤</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G10" s="60">
-        <f>IF(OR(N(E10)=0,N(F10)=0),"",E10*F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>되메우기 다짐 · 아스콘 포장</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>다짐장비</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>램머 80kg</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="59" t="n">
-        <v>180</v>
-      </c>
-      <c r="G11" s="60">
-        <f>IF(OR(N(E11)=0,N(F11)=0),"",E11*F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>되메우기 · 모래 다짐</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>다짐장비</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>플레이트 콤팩터</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="59" t="n">
-        <v>180</v>
-      </c>
-      <c r="G12" s="60">
-        <f>IF(OR(N(E12)=0,N(F12)=0),"",E12*F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>되메우기 · 모래 다짐</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>발전기</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>5kW</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="59" t="n">
-        <v>180</v>
-      </c>
-      <c r="G13" s="60">
-        <f>IF(OR(N(E13)=0,N(F13)=0),"",E13*F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>소형 전동공구 동력</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>양수기</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>3"</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="G14" s="60">
-        <f>IF(OR(N(E14)=0,N(F14)=0),"",E14*F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>양수 작업</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>덤프트럭</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>15톤</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G15" s="60">
-        <f>IF(OR(N(E15)=0,N(F15)=0),"",E15*F15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>사토 반출 · 운반</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>덤프트럭</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>5톤</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="G16" s="60">
-        <f>IF(OR(N(E16)=0,N(F16)=0),"",E16*F16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>사토 소운반</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>덤프트럭</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>1.0톤</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="G17" s="60">
-        <f>IF(OR(N(E17)=0,N(F17)=0),"",E17*F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>지선 관로 사토 · 운반</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>크레인</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="30" t="inlineStr">
-        <is>
-          <t>25톤</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="60">
-        <f>IF(OR(N(E18)=0,N(F18)=0),"",E18*F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>가시설 · 맨홀 설치</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="59" t="n"/>
-      <c r="F19" s="59" t="n"/>
-      <c r="G19" s="60">
-        <f>IF(OR(N(E19)=0,N(F19)=0),"",E19*F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="24" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="59" t="n"/>
-      <c r="F20" s="59" t="n"/>
-      <c r="G20" s="60">
-        <f>IF(OR(N(E20)=0,N(F20)=0),"",E20*F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="24" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="61">
-        <f>IF(SUM(G7:G20)=0,"",SUM(G7:G20))</f>
-        <v/>
-      </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="25" t="inlineStr"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="8" customHeight="1"/>
-    <row r="23" ht="3" customHeight="1"/>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2) 인원 투입 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>직  종</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>1일
-(인)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>투입
-일수</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>누  계
-(인·일)</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>작 업 내 용</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>직원</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="59" t="n">
-        <v>240</v>
-      </c>
-      <c r="E26" s="60">
-        <f>IF(OR(N(C26)=0,N(D26)=0),"",C26*D26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>현장 작업 지시 · 관리</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>작업반장</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" s="60">
-        <f>IF(OR(N(C27)=0,N(D27)=0),"",C27*D27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>구간별 작업 총괄</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>배관공</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="59" t="n">
-        <v>180</v>
-      </c>
-      <c r="E28" s="60">
-        <f>IF(OR(N(C28)=0,N(D28)=0),"",C28*D28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>관 부설 · 접합</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>보통인부</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="59" t="n">
-        <v>200</v>
-      </c>
-      <c r="E29" s="60">
-        <f>IF(OR(N(C29)=0,N(D29)=0),"",C29*D29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="24" t="inlineStr">
-        <is>
-          <t>현장 정리 · 기능공 보조</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>포장공</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="E30" s="60">
-        <f>IF(OR(N(C30)=0,N(D30)=0),"",C30*D30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>콘크리트 · 아스콘 포장</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>특별인부</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="E31" s="60">
-        <f>IF(OR(N(C31)=0,N(D31)=0),"",C31*D31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="24" t="inlineStr">
-        <is>
-          <t>용접공 · 기능공 보조 등 약간의 기능이 필요한 작업</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>가시설공</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="E32" s="60">
-        <f>IF(OR(N(C32)=0,N(D32)=0),"",C32*D32)</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>흙막이공</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>목공</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="59" t="n">
-        <v>40</v>
-      </c>
-      <c r="E33" s="60">
-        <f>IF(OR(N(C33)=0,N(D33)=0),"",C33*D33)</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>거푸집 제작 · 조립</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>콘크리트공</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="59" t="n">
-        <v>40</v>
-      </c>
-      <c r="E34" s="60">
-        <f>IF(OR(N(C34)=0,N(D34)=0),"",C34*D34)</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>콘크리트 타설</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="59" t="n"/>
-      <c r="D35" s="59" t="n"/>
-      <c r="E35" s="60">
-        <f>IF(OR(N(C35)=0,N(D35)=0),"",C35*D35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="59" t="n"/>
-      <c r="D36" s="59" t="n"/>
-      <c r="E36" s="60">
-        <f>IF(OR(N(C36)=0,N(D36)=0),"",C36*D36)</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="61">
-        <f>IF(SUM(E26:E36)=0,"",SUM(E26:E36))</f>
-        <v/>
-      </c>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="25" t="inlineStr"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>※ 누계 = 1일 투입 × 투입일수. 장비 · 인원은 현장 여건을 감안해 투입합니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="108">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A31:B31"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1"/>
-    <row r="3" ht="50" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>목          차</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1"/>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>공 사 개 요</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>위  치  도</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>현 장 조 직 도</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>예 정 공 정 표</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>주요 공정의 시공절차 및 방법</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>일일 시공 일정</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>7.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>주요 장비 및 인력 투입 계획</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>8.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>안전 및 환경관리 계획</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="A9:B9"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>1.  공 사 개 요</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="14">
-        <f>IF('표지'!E5="","",'표지'!E5)</f>
-        <v/>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>공사 금액</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>발 주 처</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>현장 위치</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>도급 형태</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>관할 행정기관</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>공사 기간</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="I8" s="19">
-        <f>IF(OR(N(I7)=0,N(K7)=0),"",IF(K7&lt;I7,"⚠ 준공일이 착공일보다 빠름",K7-I7+1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="3" customHeight="1"/>
-    <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>공사 개요 (주요 물량)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>공  종</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>규  격</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>수  량</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>오수관로</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>오수관로</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>오수관로</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>오수맨홀</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>개소</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="24" t="n"/>
-      <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>배수설비</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>가구</t>
-        </is>
-      </c>
-      <c r="I17" s="23" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="24" t="n"/>
-      <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>오수맨홀 펌프장</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>개소</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="24" t="n"/>
-      <c r="L18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="23" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="24" t="n"/>
-      <c r="L19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="23" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="24" t="n"/>
-      <c r="L20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>관로 연장 합계 (단위가 m 인 줄)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="26">
-        <f>IF(SUMIF(H13:H20,"m",I13:I20)=0,"",SUMIF(H13:H20,"m",I13:I20))</f>
-        <v/>
-      </c>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="25" t="inlineStr"/>
-      <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="3" customHeight="1"/>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>공사 목적</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="27">
-        <f>"    "&amp;IF(C6="","대상 지역",C6)&amp;"의 합류식 하수관로를 분류식으로 바꾸고 하수관로를 체계적으로 정비하여 마을에서 생기는 오수를 모두 차집 · 처리함으로써, 하수처리 효율을 높이고 위생적인 생활환경을 만들며 방류 수역의 수질을 지키는 데 목적이 있습니다."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="3" customHeight="1"/>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>특이 사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>하늘색 칸 = 자동(공사명 · 공사 일수 · 관로 연장 합계 · 목적 글).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="I5:L5"/>
-  </mergeCells>
-  <conditionalFormatting sqref="I13:I20">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(I13),MOD(I13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(ISNUMBER(I21),MOD(I21,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9155,10 +5363,7 @@
           <t>착 공 일</t>
         </is>
       </c>
-      <c r="B3" s="35">
-        <f>IF(N('1.공사개요'!I7)=0,"",'1.공사개요'!I7)</f>
-        <v/>
-      </c>
+      <c r="B3" s="35" t="n"/>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="10" t="inlineStr">
         <is>
@@ -9187,65 +5392,29 @@
           <t>일 수</t>
         </is>
       </c>
-      <c r="E4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
+      <c r="E4" s="36" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
+      <c r="G4" s="36" t="n"/>
       <c r="H4" s="6" t="n"/>
-      <c r="I4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
+      <c r="I4" s="36" t="n"/>
       <c r="J4" s="6" t="n"/>
-      <c r="K4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
+      <c r="K4" s="36" t="n"/>
       <c r="L4" s="6" t="n"/>
-      <c r="M4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
+      <c r="M4" s="36" t="n"/>
       <c r="N4" s="6" t="n"/>
-      <c r="O4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
+      <c r="O4" s="36" t="n"/>
       <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
+      <c r="Q4" s="36" t="n"/>
       <c r="R4" s="6" t="n"/>
-      <c r="S4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
+      <c r="S4" s="36" t="n"/>
       <c r="T4" s="6" t="n"/>
-      <c r="U4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
+      <c r="U4" s="36" t="n"/>
       <c r="V4" s="6" t="n"/>
-      <c r="W4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
+      <c r="W4" s="36" t="n"/>
       <c r="X4" s="6" t="n"/>
-      <c r="Y4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
+      <c r="Y4" s="36" t="n"/>
       <c r="Z4" s="6" t="n"/>
-      <c r="AA4" s="36">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
+      <c r="AA4" s="36" t="n"/>
       <c r="AB4" s="6" t="n"/>
       <c r="AC4" s="21" t="inlineStr">
         <is>
@@ -9381,200 +5550,56 @@
       <c r="AC5" s="6" t="n"/>
     </row>
     <row r="6" hidden="1" ht="12" customHeight="1">
-      <c r="E6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+15)</f>
-        <v/>
-      </c>
-      <c r="G6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="H6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+15)</f>
-        <v/>
-      </c>
-      <c r="I6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="J6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+15)</f>
-        <v/>
-      </c>
-      <c r="K6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="L6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+15)</f>
-        <v/>
-      </c>
-      <c r="M6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="N6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+15)</f>
-        <v/>
-      </c>
-      <c r="O6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="P6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+15)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="R6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+15)</f>
-        <v/>
-      </c>
-      <c r="S6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="T6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+15)</f>
-        <v/>
-      </c>
-      <c r="U6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="V6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+15)</f>
-        <v/>
-      </c>
-      <c r="W6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="X6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+15)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+15)</f>
-        <v/>
-      </c>
-      <c r="AA6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+15)</f>
-        <v/>
-      </c>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="38" t="n"/>
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="38" t="n"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="38" t="n"/>
+      <c r="O6" s="38" t="n"/>
+      <c r="P6" s="38" t="n"/>
+      <c r="Q6" s="38" t="n"/>
+      <c r="R6" s="38" t="n"/>
+      <c r="S6" s="38" t="n"/>
+      <c r="T6" s="38" t="n"/>
+      <c r="U6" s="38" t="n"/>
+      <c r="V6" s="38" t="n"/>
+      <c r="W6" s="38" t="n"/>
+      <c r="X6" s="38" t="n"/>
+      <c r="Y6" s="38" t="n"/>
+      <c r="Z6" s="38" t="n"/>
+      <c r="AA6" s="38" t="n"/>
+      <c r="AB6" s="38" t="n"/>
     </row>
     <row r="7" hidden="1" ht="12" customHeight="1">
-      <c r="E7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+14)</f>
-        <v/>
-      </c>
-      <c r="F7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)-1)</f>
-        <v/>
-      </c>
-      <c r="G7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+14)</f>
-        <v/>
-      </c>
-      <c r="H7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)-1)</f>
-        <v/>
-      </c>
-      <c r="I7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+14)</f>
-        <v/>
-      </c>
-      <c r="J7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)-1)</f>
-        <v/>
-      </c>
-      <c r="K7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+14)</f>
-        <v/>
-      </c>
-      <c r="L7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)-1)</f>
-        <v/>
-      </c>
-      <c r="M7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+14)</f>
-        <v/>
-      </c>
-      <c r="N7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)-1)</f>
-        <v/>
-      </c>
-      <c r="O7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+14)</f>
-        <v/>
-      </c>
-      <c r="P7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)-1)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+14)</f>
-        <v/>
-      </c>
-      <c r="R7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)-1)</f>
-        <v/>
-      </c>
-      <c r="S7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+14)</f>
-        <v/>
-      </c>
-      <c r="T7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)-1)</f>
-        <v/>
-      </c>
-      <c r="U7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+14)</f>
-        <v/>
-      </c>
-      <c r="V7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)-1)</f>
-        <v/>
-      </c>
-      <c r="W7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+14)</f>
-        <v/>
-      </c>
-      <c r="X7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)-1)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+14)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)-1)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+14)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="38">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),12)-1)</f>
-        <v/>
-      </c>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="38" t="n"/>
+      <c r="Q7" s="38" t="n"/>
+      <c r="R7" s="38" t="n"/>
+      <c r="S7" s="38" t="n"/>
+      <c r="T7" s="38" t="n"/>
+      <c r="U7" s="38" t="n"/>
+      <c r="V7" s="38" t="n"/>
+      <c r="W7" s="38" t="n"/>
+      <c r="X7" s="38" t="n"/>
+      <c r="Y7" s="38" t="n"/>
+      <c r="Z7" s="38" t="n"/>
+      <c r="AA7" s="38" t="n"/>
+      <c r="AB7" s="38" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -9584,10 +5609,7 @@
       </c>
       <c r="B8" s="39" t="n"/>
       <c r="C8" s="39" t="n"/>
-      <c r="D8" s="40">
-        <f>IF(OR(N(B8)=0,N(C8)=0),"",IF(C8&lt;B8,"⚠",C8-B8+1))</f>
-        <v/>
-      </c>
+      <c r="D8" s="40" t="n"/>
       <c r="E8" s="41" t="inlineStr"/>
       <c r="F8" s="41" t="inlineStr"/>
       <c r="G8" s="41" t="inlineStr"/>
@@ -9622,10 +5644,7 @@
       </c>
       <c r="B9" s="39" t="n"/>
       <c r="C9" s="39" t="n"/>
-      <c r="D9" s="40">
-        <f>IF(OR(N(B9)=0,N(C9)=0),"",IF(C9&lt;B9,"⚠",C9-B9+1))</f>
-        <v/>
-      </c>
+      <c r="D9" s="40" t="n"/>
       <c r="E9" s="41" t="inlineStr"/>
       <c r="F9" s="41" t="inlineStr"/>
       <c r="G9" s="41" t="inlineStr"/>
@@ -9660,10 +5679,7 @@
       </c>
       <c r="B10" s="39" t="n"/>
       <c r="C10" s="39" t="n"/>
-      <c r="D10" s="40">
-        <f>IF(OR(N(B10)=0,N(C10)=0),"",IF(C10&lt;B10,"⚠",C10-B10+1))</f>
-        <v/>
-      </c>
+      <c r="D10" s="40" t="n"/>
       <c r="E10" s="41" t="inlineStr"/>
       <c r="F10" s="41" t="inlineStr"/>
       <c r="G10" s="41" t="inlineStr"/>
@@ -9698,10 +5714,7 @@
       </c>
       <c r="B11" s="39" t="n"/>
       <c r="C11" s="39" t="n"/>
-      <c r="D11" s="40">
-        <f>IF(OR(N(B11)=0,N(C11)=0),"",IF(C11&lt;B11,"⚠",C11-B11+1))</f>
-        <v/>
-      </c>
+      <c r="D11" s="40" t="n"/>
       <c r="E11" s="41" t="inlineStr"/>
       <c r="F11" s="41" t="inlineStr"/>
       <c r="G11" s="41" t="inlineStr"/>
@@ -9736,10 +5749,7 @@
       </c>
       <c r="B12" s="39" t="n"/>
       <c r="C12" s="39" t="n"/>
-      <c r="D12" s="40">
-        <f>IF(OR(N(B12)=0,N(C12)=0),"",IF(C12&lt;B12,"⚠",C12-B12+1))</f>
-        <v/>
-      </c>
+      <c r="D12" s="40" t="n"/>
       <c r="E12" s="41" t="inlineStr"/>
       <c r="F12" s="41" t="inlineStr"/>
       <c r="G12" s="41" t="inlineStr"/>
@@ -9774,10 +5784,7 @@
       </c>
       <c r="B13" s="39" t="n"/>
       <c r="C13" s="39" t="n"/>
-      <c r="D13" s="40">
-        <f>IF(OR(N(B13)=0,N(C13)=0),"",IF(C13&lt;B13,"⚠",C13-B13+1))</f>
-        <v/>
-      </c>
+      <c r="D13" s="40" t="n"/>
       <c r="E13" s="41" t="inlineStr"/>
       <c r="F13" s="41" t="inlineStr"/>
       <c r="G13" s="41" t="inlineStr"/>
@@ -9812,10 +5819,7 @@
       </c>
       <c r="B14" s="39" t="n"/>
       <c r="C14" s="39" t="n"/>
-      <c r="D14" s="40">
-        <f>IF(OR(N(B14)=0,N(C14)=0),"",IF(C14&lt;B14,"⚠",C14-B14+1))</f>
-        <v/>
-      </c>
+      <c r="D14" s="40" t="n"/>
       <c r="E14" s="41" t="inlineStr"/>
       <c r="F14" s="41" t="inlineStr"/>
       <c r="G14" s="41" t="inlineStr"/>
@@ -9850,10 +5854,7 @@
       </c>
       <c r="B15" s="39" t="n"/>
       <c r="C15" s="39" t="n"/>
-      <c r="D15" s="40">
-        <f>IF(OR(N(B15)=0,N(C15)=0),"",IF(C15&lt;B15,"⚠",C15-B15+1))</f>
-        <v/>
-      </c>
+      <c r="D15" s="40" t="n"/>
       <c r="E15" s="41" t="inlineStr"/>
       <c r="F15" s="41" t="inlineStr"/>
       <c r="G15" s="41" t="inlineStr"/>
@@ -9888,10 +5889,7 @@
       </c>
       <c r="B16" s="39" t="n"/>
       <c r="C16" s="39" t="n"/>
-      <c r="D16" s="40">
-        <f>IF(OR(N(B16)=0,N(C16)=0),"",IF(C16&lt;B16,"⚠",C16-B16+1))</f>
-        <v/>
-      </c>
+      <c r="D16" s="40" t="n"/>
       <c r="E16" s="41" t="inlineStr"/>
       <c r="F16" s="41" t="inlineStr"/>
       <c r="G16" s="41" t="inlineStr"/>
@@ -9922,10 +5920,7 @@
       <c r="A17" s="24" t="n"/>
       <c r="B17" s="39" t="n"/>
       <c r="C17" s="39" t="n"/>
-      <c r="D17" s="40">
-        <f>IF(OR(N(B17)=0,N(C17)=0),"",IF(C17&lt;B17,"⚠",C17-B17+1))</f>
-        <v/>
-      </c>
+      <c r="D17" s="40" t="n"/>
       <c r="E17" s="41" t="inlineStr"/>
       <c r="F17" s="41" t="inlineStr"/>
       <c r="G17" s="41" t="inlineStr"/>
@@ -9956,10 +5951,7 @@
       <c r="A18" s="24" t="n"/>
       <c r="B18" s="39" t="n"/>
       <c r="C18" s="39" t="n"/>
-      <c r="D18" s="40">
-        <f>IF(OR(N(B18)=0,N(C18)=0),"",IF(C18&lt;B18,"⚠",C18-B18+1))</f>
-        <v/>
-      </c>
+      <c r="D18" s="40" t="n"/>
       <c r="E18" s="41" t="inlineStr"/>
       <c r="F18" s="41" t="inlineStr"/>
       <c r="G18" s="41" t="inlineStr"/>
@@ -10019,11 +6011,6 @@
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="E8:AB18">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(N($B8)&gt;0,N($C8)&gt;=N($B8),$B8&lt;=E$7,$C8&gt;=E$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/public/forms/hasugwangeo-sigong.xlsx
+++ b/web/public/forms/hasugwangeo-sigong.xlsx
@@ -1233,7 +1233,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3355,7 +3355,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
